--- a/Data/mappings/exiobase/EXIO_3_9_IW_concordance.xlsx
+++ b/Data/mappings/exiobase/EXIO_3_9_IW_concordance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11max\PycharmProjects\IW_Reborn\Data\mappings\exiobase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9B44C6-0B0B-4A46-98EE-6FCAB3004781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{605C0B57-8B88-4143-A68F-BC438824E773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="800">
   <si>
     <t>Artificial Surfaces</t>
   </si>
@@ -2345,6 +2345,81 @@
   </si>
   <si>
     <t>Zinc(II)</t>
+  </si>
+  <si>
+    <t>Wood, soft, standing</t>
+  </si>
+  <si>
+    <t>Oil, crude</t>
+  </si>
+  <si>
+    <t>Coal, hard</t>
+  </si>
+  <si>
+    <t>Coal, brown</t>
+  </si>
+  <si>
+    <t>Gas, natural/m3</t>
+  </si>
+  <si>
+    <t>Peat</t>
+  </si>
+  <si>
+    <t>Bauxite</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Lead</t>
+  </si>
+  <si>
+    <t>Nickel</t>
+  </si>
+  <si>
+    <t>Magnesium</t>
+  </si>
+  <si>
+    <t>Platinum</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Tin</t>
+  </si>
+  <si>
+    <t>Uranium</t>
+  </si>
+  <si>
+    <t>Zinc</t>
+  </si>
+  <si>
+    <t>Salt, unspecified</t>
+  </si>
+  <si>
+    <t>Limestone</t>
+  </si>
+  <si>
+    <t>Gravel</t>
+  </si>
+  <si>
+    <t>Dolomite</t>
+  </si>
+  <si>
+    <t>Gypsum</t>
+  </si>
+  <si>
+    <t>Clay, unspecified</t>
+  </si>
+  <si>
+    <t>Carbon monoxide, biogenic</t>
   </si>
 </sst>
 </file>
@@ -3042,7 +3117,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>743</v>
+        <v>799</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -3050,7 +3125,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>743</v>
+        <v>799</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -3058,7 +3133,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>743</v>
+        <v>799</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -3665,278 +3740,368 @@
       <c r="A121" s="3" t="s">
         <v>119</v>
       </c>
+      <c r="B121" s="3" t="s">
+        <v>775</v>
+      </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>120</v>
       </c>
+      <c r="B122" s="3" t="s">
+        <v>775</v>
+      </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
         <v>121</v>
       </c>
+      <c r="B123" s="3" t="s">
+        <v>777</v>
+      </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>122</v>
       </c>
+      <c r="B124" s="3" t="s">
+        <v>777</v>
+      </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>123</v>
       </c>
+      <c r="B125" s="3" t="s">
+        <v>776</v>
+      </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
         <v>124</v>
       </c>
+      <c r="B126" s="3" t="s">
+        <v>778</v>
+      </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
         <v>125</v>
       </c>
+      <c r="B127" s="3" t="s">
+        <v>779</v>
+      </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B130" s="3" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B131" s="3" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B132" s="3" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B134" s="3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B136" s="3" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B137" s="3" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B138" s="3" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B139" s="3" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B141" s="3" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B142" s="3" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B143" s="3" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B144" s="3" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B145" s="3" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B147" s="3" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B148" s="3" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B151" s="3" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B153" s="3" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B155" s="3" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B156" s="3" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B159" s="3" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B160" s="3" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B161" s="3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B162" s="3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
         <v>174</v>
       </c>
